--- a/dataset/01.w_Defects/unlock_without_lock.xlsx
+++ b/dataset/01.w_Defects/unlock_without_lock.xlsx
@@ -495,7 +495,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>pthread_mutex_t unlock_without_lock_001_glb_mutex = PTHREAD_MUTEX_INITIALIZER; int unlock_without_lock_001_glb_data = 0; pthread_mutex_t unlock_without_lock_002_glb_mutex = PTHREAD_MUTEX_INITIALIZER; unsigned long unlock_without_lock_002_glb_data = 0; int const unlock_without_lock_002_var = 10; pthread_mutex_t unlock_without_lock_003_glb_mutex = PTHREAD_MUTEX_INITIALIZER; float unlock_without_lock_003_glb_data = 1000.0; pthread_mutex_t unlock_without_lock_004_glb_mutex_1 = PTHREAD_MUTEX_INITIALIZER; pthread_mutex_t unlock_without_lock_004_glb_mutex_2 = PTHREAD_MUTEX_INITIALIZER; int lock_never_unlock_004_glb_var = 0; pthread_mutex_t unlock_without_lock_005_glb_mutex = PTHREAD_MUTEX_INITIALIZER; int unlock_without_lock_005_glb_data = 0; int unlock_without_lock_005_thread_set = 1; pthread_mutex_t unlock_without_lock_006_glb_mutex_1 = PTHREAD_MUTEX_INITIALIZER; pthread_mutex_t unlock_without_lock_006_glb_mutex_2 = PTHREAD_MUTEX_INITIALIZER; char unlock_without_lock_006_glb_buf[5]="BBBBB"; pthread_mutex_t unlock_without_lock_007_glb_mutex_1 = PTHREAD_MUTEX_INITIALIZER; pthread_mutex_t unlock_without_lock_007_glb_mutex_2 = PTHREAD_MUTEX_INITIALIZER; int unlock_without_lock_007_glb_var = 0; pthread_mutex_t unlock_without_lock_008_glb_mutex_1 = PTHREAD_MUTEX_INITIALIZER; pthread_mutex_t unlock_without_lock_008_glb_mutex_2 = PTHREAD_MUTEX_INITIALIZER; int unlock_without_lock_008_glb_var = 0; extern volatile int vflag; void unlock_without_lock_003 () { #if ! defined(CHECKER_POLYSPACE) pthread_t tid1,tid2; intptr_t t1 = 10, t2 = 20; pthread_mutex_init(&amp;unlock_without_lock_003_glb_mutex, NULL); pthread_create(&amp;tid1, NULL, unlock_without_lock_003_tsk_001, (void *)t1); pthread_create(&amp;tid2, NULL, unlock_without_lock_003_tsk_001, (void *)t2); pthread_join(tid1, NULL); pthread_join(tid2, NULL); pthread_mutex_destroy(&amp;unlock_without_lock_003_glb_mutex); #endif /* defined(CHECKER_POLYSPACE) */ } void* unlock_without_lock_003_tsk_001 (void *pram) { #if ! defined(CHECKER_POLYSPACE) if(unlock_without_lock_003_func_002(10) &gt;1) { pthread_mutex_lock (&amp;unlock_without_lock_003_glb_mutex); } unlock_without_lock_003_glb_data = (unlock_without_lock_003_glb_data) + 3.5; unlock_without_lock_003_func_001(pram); if(unlock_without_lock_003_func_002(10) &gt; 1) { pthread_mutex_unlock(&amp;unlock_without_lock_003_glb_mutex); } #endif /* defined(CHECKER_POLYSPACE) */ return NULL; } int unlock_without_lock_003_func_002 (int a ) { int ret = 0; if (a &gt; 1) { ret = a++; } else { ret = 0; } return ret; } void unlock_without_lock_003_func_001 (void *pram) { #if ! defined(CHECKER_POLYSPACE) if(unlock_without_lock_003_func_002(0) &gt;1) { pthread_mutex_lock (&amp;unlock_without_lock_003_glb_mutex);/*Tool should detect this line as error*/ /* ERROR:UnLock without lock */ } unlock_without_lock_003_glb_data = (unlock_without_lock_003_glb_data) + 1.2; #if defined PRINT_DEBUG int ip = (intptr_t)pram; printf("Task3! Unlock without Lock, thread # %d! gbl3 = %f \n",ip ,unlock_without_lock_003_glb_data); #endif /* defined(PRINT_DEBUG) */ unlock_without_lock_003_func_002(10); if(unlock_without_lock_003_func_002(10) &gt;1) { pthread_mutex_unlock (&amp;unlock_without_lock_003_glb_mutex); } #endif /* ! defined(CHECKER_POLYSPACE) */ }</t>
+          <t>pthread_mutex_t unlock_without_lock_001_glb_mutex = PTHREAD_MUTEX_INITIALIZER; int unlock_without_lock_001_glb_data = 0; pthread_mutex_t unlock_without_lock_002_glb_mutex = PTHREAD_MUTEX_INITIALIZER; unsigned long unlock_without_lock_002_glb_data = 0; int const unlock_without_lock_002_var = 10; pthread_mutex_t unlock_without_lock_003_glb_mutex = PTHREAD_MUTEX_INITIALIZER; float unlock_without_lock_003_glb_data = 1000.0; pthread_mutex_t unlock_without_lock_004_glb_mutex_1 = PTHREAD_MUTEX_INITIALIZER; pthread_mutex_t unlock_without_lock_004_glb_mutex_2 = PTHREAD_MUTEX_INITIALIZER; int lock_never_unlock_004_glb_var = 0; pthread_mutex_t unlock_without_lock_005_glb_mutex = PTHREAD_MUTEX_INITIALIZER; int unlock_without_lock_005_glb_data = 0; int unlock_without_lock_005_thread_set = 1; pthread_mutex_t unlock_without_lock_006_glb_mutex_1 = PTHREAD_MUTEX_INITIALIZER; pthread_mutex_t unlock_without_lock_006_glb_mutex_2 = PTHREAD_MUTEX_INITIALIZER; char unlock_without_lock_006_glb_buf[5]="BBBBB"; pthread_mutex_t unlock_without_lock_007_glb_mutex_1 = PTHREAD_MUTEX_INITIALIZER; pthread_mutex_t unlock_without_lock_007_glb_mutex_2 = PTHREAD_MUTEX_INITIALIZER; int unlock_without_lock_007_glb_var = 0; pthread_mutex_t unlock_without_lock_008_glb_mutex_1 = PTHREAD_MUTEX_INITIALIZER; pthread_mutex_t unlock_without_lock_008_glb_mutex_2 = PTHREAD_MUTEX_INITIALIZER; int unlock_without_lock_008_glb_var = 0; extern volatile int vflag; void unlock_without_lock_003 () { #if ! defined(CHECKER_POLYSPACE) pthread_t tid1,tid2; intptr_t t1 = 10, t2 = 20; pthread_mutex_init(&amp;unlock_without_lock_003_glb_mutex, NULL); pthread_create(&amp;tid1, NULL, unlock_without_lock_003_tsk_001, (void *)t1); pthread_create(&amp;tid2, NULL, unlock_without_lock_003_tsk_001, (void *)t2); pthread_join(tid1, NULL); pthread_join(tid2, NULL); pthread_mutex_destroy(&amp;unlock_without_lock_003_glb_mutex); #endif /* defined(CHECKER_POLYSPACE) */ } void* unlock_without_lock_003_tsk_001 (void *pram) { #if ! defined(CHECKER_POLYSPACE) if(unlock_without_lock_003_func_002(10) &gt;1) { pthread_mutex_lock (&amp;unlock_without_lock_003_glb_mutex); } unlock_without_lock_003_glb_data = (unlock_without_lock_003_glb_data) + 3.5; unlock_without_lock_003_func_001(pram); if(unlock_without_lock_003_func_002(10) &gt; 1) { pthread_mutex_unlock(&amp;unlock_without_lock_003_glb_mutex); } #endif /* defined(CHECKER_POLYSPACE) */ return NULL; } void unlock_without_lock_003_func_001 (void *pram) { #if ! defined(CHECKER_POLYSPACE) if(unlock_without_lock_003_func_002(0) &gt;1) { pthread_mutex_lock (&amp;unlock_without_lock_003_glb_mutex);/*Tool should detect this line as error*/ /* ERROR:UnLock without lock */ } unlock_without_lock_003_glb_data = (unlock_without_lock_003_glb_data) + 1.2; #if defined PRINT_DEBUG int ip = (intptr_t)pram; printf("Task3! Unlock without Lock, thread # %d! gbl3 = %f \n",ip ,unlock_without_lock_003_glb_data); #endif /* defined(PRINT_DEBUG) */ unlock_without_lock_003_func_002(10); if(unlock_without_lock_003_func_002(10) &gt;1) { pthread_mutex_unlock (&amp;unlock_without_lock_003_glb_mutex); } #endif /* ! defined(CHECKER_POLYSPACE) */ } int unlock_without_lock_003_func_002 (int a ) { int ret = 0; if (a &gt; 1) { ret = a++; } else { ret = 0; } return ret; }</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -605,7 +605,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>pthread_mutex_t unlock_without_lock_001_glb_mutex = PTHREAD_MUTEX_INITIALIZER; int unlock_without_lock_001_glb_data = 0; pthread_mutex_t unlock_without_lock_002_glb_mutex = PTHREAD_MUTEX_INITIALIZER; unsigned long unlock_without_lock_002_glb_data = 0; int const unlock_without_lock_002_var = 10; pthread_mutex_t unlock_without_lock_003_glb_mutex = PTHREAD_MUTEX_INITIALIZER; float unlock_without_lock_003_glb_data = 1000.0; pthread_mutex_t unlock_without_lock_004_glb_mutex_1 = PTHREAD_MUTEX_INITIALIZER; pthread_mutex_t unlock_without_lock_004_glb_mutex_2 = PTHREAD_MUTEX_INITIALIZER; int lock_never_unlock_004_glb_var = 0; pthread_mutex_t unlock_without_lock_005_glb_mutex = PTHREAD_MUTEX_INITIALIZER; int unlock_without_lock_005_glb_data = 0; int unlock_without_lock_005_thread_set = 1; pthread_mutex_t unlock_without_lock_006_glb_mutex_1 = PTHREAD_MUTEX_INITIALIZER; pthread_mutex_t unlock_without_lock_006_glb_mutex_2 = PTHREAD_MUTEX_INITIALIZER; char unlock_without_lock_006_glb_buf[5]="BBBBB"; pthread_mutex_t unlock_without_lock_007_glb_mutex_1 = PTHREAD_MUTEX_INITIALIZER; pthread_mutex_t unlock_without_lock_007_glb_mutex_2 = PTHREAD_MUTEX_INITIALIZER; int unlock_without_lock_007_glb_var = 0; pthread_mutex_t unlock_without_lock_008_glb_mutex_1 = PTHREAD_MUTEX_INITIALIZER; pthread_mutex_t unlock_without_lock_008_glb_mutex_2 = PTHREAD_MUTEX_INITIALIZER; int unlock_without_lock_008_glb_var = 0; extern volatile int vflag; void unlock_without_lock_008 () { #if ! defined(CHECKER_POLYSPACE) pthread_t th1,th2; intptr_t t1 = 10; intptr_t t2 = 20; pthread_create(&amp;th1, NULL, unlock_without_lock_008_tsk_001, (void *)t1); pthread_create(&amp;th2, NULL, unlock_without_lock_008_tsk_002, (void *)t2); pthread_join(th1, NULL); pthread_join(th2, NULL); #endif /* defined(CHECKER_POLYSPACE) */ } void * unlock_without_lock_008_tsk_002(void *input) { #if ! defined(CHECKER_POLYSPACE) long ip; int i=5; ip = (long)input; ip = ip *20; do { if (ip &gt;= 0) { if(i!=5) { pthread_mutex_lock( &amp;unlock_without_lock_008_glb_mutex_2 ); unlock_without_lock_008_glb_var += 20; pthread_mutex_unlock( &amp;unlock_without_lock_008_glb_mutex_2 ); } pthread_mutex_unlock( &amp;unlock_without_lock_008_glb_mutex_2 );/*Tool should detect this line as error*/ /* ERROR:Unlock without Lock */ } i--; } while (i&gt;0); #if defined PRINT_DEBUG printf("Task8_2! Unlock without Lock, thread #%ld!\n",ip); #endif /* defined(PRINT_DEBUG) */ #endif /* defined(CHECKER_POLYSPACE) */ return NULL; } void *unlock_without_lock_008_tsk_001(void *input) { #if ! defined(CHECKER_POLYSPACE) long ip; int i = 5; ip = (long)input; ip = ip *10; do { if (ip &gt;= 0) { pthread_mutex_lock( &amp;unlock_without_lock_008_glb_mutex_1 ); unlock_without_lock_008_glb_var += 10; pthread_mutex_unlock( &amp;unlock_without_lock_008_glb_mutex_1 ); } i--; }while (i&gt;0); #if defined PRINT_DEBUG printf("Task8_1! Unlock without Lock, thread #%ld!\n",ip); #endif /* defined(PRINT_DEBUG) */ #endif /* defined(CHECKER_POLYSPACE) */ return NULL; }</t>
+          <t>pthread_mutex_t unlock_without_lock_001_glb_mutex = PTHREAD_MUTEX_INITIALIZER; int unlock_without_lock_001_glb_data = 0; pthread_mutex_t unlock_without_lock_002_glb_mutex = PTHREAD_MUTEX_INITIALIZER; unsigned long unlock_without_lock_002_glb_data = 0; int const unlock_without_lock_002_var = 10; pthread_mutex_t unlock_without_lock_003_glb_mutex = PTHREAD_MUTEX_INITIALIZER; float unlock_without_lock_003_glb_data = 1000.0; pthread_mutex_t unlock_without_lock_004_glb_mutex_1 = PTHREAD_MUTEX_INITIALIZER; pthread_mutex_t unlock_without_lock_004_glb_mutex_2 = PTHREAD_MUTEX_INITIALIZER; int lock_never_unlock_004_glb_var = 0; pthread_mutex_t unlock_without_lock_005_glb_mutex = PTHREAD_MUTEX_INITIALIZER; int unlock_without_lock_005_glb_data = 0; int unlock_without_lock_005_thread_set = 1; pthread_mutex_t unlock_without_lock_006_glb_mutex_1 = PTHREAD_MUTEX_INITIALIZER; pthread_mutex_t unlock_without_lock_006_glb_mutex_2 = PTHREAD_MUTEX_INITIALIZER; char unlock_without_lock_006_glb_buf[5]="BBBBB"; pthread_mutex_t unlock_without_lock_007_glb_mutex_1 = PTHREAD_MUTEX_INITIALIZER; pthread_mutex_t unlock_without_lock_007_glb_mutex_2 = PTHREAD_MUTEX_INITIALIZER; int unlock_without_lock_007_glb_var = 0; pthread_mutex_t unlock_without_lock_008_glb_mutex_1 = PTHREAD_MUTEX_INITIALIZER; pthread_mutex_t unlock_without_lock_008_glb_mutex_2 = PTHREAD_MUTEX_INITIALIZER; int unlock_without_lock_008_glb_var = 0; extern volatile int vflag; void unlock_without_lock_008 () { #if ! defined(CHECKER_POLYSPACE) pthread_t th1,th2; intptr_t t1 = 10; intptr_t t2 = 20; pthread_create(&amp;th1, NULL, unlock_without_lock_008_tsk_001, (void *)t1); pthread_create(&amp;th2, NULL, unlock_without_lock_008_tsk_002, (void *)t2); pthread_join(th1, NULL); pthread_join(th2, NULL); #endif /* defined(CHECKER_POLYSPACE) */ } void *unlock_without_lock_008_tsk_001(void *input) { #if ! defined(CHECKER_POLYSPACE) long ip; int i = 5; ip = (long)input; ip = ip *10; do { if (ip &gt;= 0) { pthread_mutex_lock( &amp;unlock_without_lock_008_glb_mutex_1 ); unlock_without_lock_008_glb_var += 10; pthread_mutex_unlock( &amp;unlock_without_lock_008_glb_mutex_1 ); } i--; }while (i&gt;0); #if defined PRINT_DEBUG printf("Task8_1! Unlock without Lock, thread #%ld!\n",ip); #endif /* defined(PRINT_DEBUG) */ #endif /* defined(CHECKER_POLYSPACE) */ return NULL; } void * unlock_without_lock_008_tsk_002(void *input) { #if ! defined(CHECKER_POLYSPACE) long ip; int i=5; ip = (long)input; ip = ip *20; do { if (ip &gt;= 0) { if(i!=5) { pthread_mutex_lock( &amp;unlock_without_lock_008_glb_mutex_2 ); unlock_without_lock_008_glb_var += 20; pthread_mutex_unlock( &amp;unlock_without_lock_008_glb_mutex_2 ); } pthread_mutex_unlock( &amp;unlock_without_lock_008_glb_mutex_2 );/*Tool should detect this line as error*/ /* ERROR:Unlock without Lock */ } i--; } while (i&gt;0); #if defined PRINT_DEBUG printf("Task8_2! Unlock without Lock, thread #%ld!\n",ip); #endif /* defined(PRINT_DEBUG) */ #endif /* defined(CHECKER_POLYSPACE) */ return NULL; }</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
